--- a/output/pdf_financials_xlsx/ALV.xlsx
+++ b/output/pdf_financials_xlsx/ALV.xlsx
@@ -869,31 +869,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>7.82</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>33.158</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>19.148</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>13.519</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>7.672</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>4.956</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>5.411</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>8.132</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>20.926</v>
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.068</v>
+        <v>-0.282</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.28</v>
+        <v>-6.54</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E348" s="5" t="n">
